--- a/output/pdf_financials_xlsx/AUAU.xlsx
+++ b/output/pdf_financials_xlsx/AUAU.xlsx
@@ -3478,25 +3478,25 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.062637</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>5.161075</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>4.643945</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>5.999061</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>6.37032</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>6.666547</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>7.404873</v>
       </c>
     </row>
     <row r="93">
@@ -4316,19 +4316,19 @@
         <v>-1.527885</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>1.642394</v>
+        <v>-0.576236</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.006935</v>
+        <v>-3.990765</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-2.844036</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.168455</v>
+        <v>-1.815783</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.176164</v>
+        <v>-1.939794</v>
       </c>
     </row>
     <row r="119">
@@ -5778,7 +5778,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -6580,7 +6584,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -7654,7 +7662,11 @@
           <t>Reserves (note 10)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -8176,7 +8188,11 @@
           <t>Reserves (note 9)</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -8842,7 +8858,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AUAU.xlsx
+++ b/output/pdf_financials_xlsx/AUAU.xlsx
@@ -780,25 +780,25 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.027833</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.025634</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.04373</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.07037400000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.016901</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.036984</v>
       </c>
     </row>
     <row r="13">
@@ -1303,25 +1303,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.865015</v>
+        <v>-3.892848</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.384503</v>
+        <v>-2.410137</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-2.850899</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.731825</v>
+        <v>-1.775555</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.47465</v>
+        <v>0.404276</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.507343</v>
+        <v>1.490442</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.485628</v>
+        <v>-2.522612</v>
       </c>
     </row>
     <row r="28">
@@ -1369,25 +1369,25 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.865015</v>
+        <v>-3.892848</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.384503</v>
+        <v>-2.410137</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.822676</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.703312</v>
+        <v>-1.747042</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.504766</v>
+        <v>0.434392</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.525011</v>
+        <v>1.50811</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.485628</v>
+        <v>-2.522612</v>
       </c>
     </row>
     <row r="30">
@@ -1536,19 +1536,19 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.813894</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.401455</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>4.256565</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>4.07633</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.239459</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.894153</v>
@@ -1602,19 +1602,19 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.813894</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.652153</v>
+        <v>1.053608</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.555424</v>
+        <v>4.811989</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.903234</v>
+        <v>4.979564</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>2.152716</v>
+        <v>2.392175</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>2.884586</v>
@@ -1998,19 +1998,19 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.8928</v>
+        <v>0.078906</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.434486</v>
+        <v>0.033031</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.277629</v>
+        <v>0.021064</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>4.199028</v>
+        <v>0.122698</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.335585</v>
+        <v>0.096126</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.165847</v>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -16472,7 +16472,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">

--- a/output/pdf_financials_xlsx/AUAU.xlsx
+++ b/output/pdf_financials_xlsx/AUAU.xlsx
@@ -615,25 +615,25 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.692603</v>
+        <v>0.837603</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.32519</v>
+        <v>0.50519</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.598627</v>
+        <v>0.7264659999999999</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.759977</v>
+        <v>0.877977</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.636772</v>
+        <v>0.763449</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.077995</v>
+        <v>1.172412</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.349231</v>
+        <v>1.446231</v>
       </c>
     </row>
     <row r="8">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.692603</v>
+        <v>0.837603</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.32519</v>
+        <v>0.50519</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>1.042486</v>
@@ -4046,25 +4046,25 @@
         </is>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.178401</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.146143</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.016479</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.003426</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.006369</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.009114000000000001</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.006582</v>
       </c>
     </row>
     <row r="111">
@@ -8248,7 +8248,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -8302,7 +8306,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -9170,7 +9178,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -10266,7 +10278,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -10488,7 +10504,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -13694,7 +13714,11 @@
           <t>Director fees (Note 10)</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -14876,7 +14900,11 @@
           <t>Director fees (Note 11)</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -16024,7 +16052,11 @@
           <t>Directors fees (note 11)</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -17034,7 +17066,11 @@
           <t>Directors fees (note 10)</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
